--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486557_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486557_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4838</v>
+        <v>4.6361</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1417</v>
+        <v>1.6947</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3421</v>
+        <v>2.9414</v>
       </c>
       <c r="G2" t="n">
         <v>2.5778</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9284</v>
+        <v>1.0806</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8857</v>
+        <v>0.4386</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0427</v>
+        <v>0.642</v>
       </c>
       <c r="V2" t="n">
         <v>0.7602</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7297</v>
+        <v>2.61</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2117</v>
+        <v>2.5093</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.482</v>
+        <v>0.1007</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4028</v>
+        <v>2.6152</v>
       </c>
       <c r="H3" t="n">
-        <v>2.786</v>
+        <v>1.2805</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6168</v>
+        <v>1.3347</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5735</v>
+        <v>2.5045</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0873</v>
+        <v>1.2989</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4862</v>
+        <v>1.2057</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1707</v>
+        <v>0.1107</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3013</v>
+        <v>-0.0184</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8694</v>
+        <v>0.1291</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8495</v>
+        <v>0.2548</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1406</v>
+        <v>0.0048</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7089</v>
+        <v>0.2499</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1562</v>
+        <v>2.4722</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7908</v>
+        <v>2.0143</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3654</v>
+        <v>0.4579</v>
       </c>
       <c r="G4" t="n">
         <v>4.1391</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0616</v>
+        <v>0.3776</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2091</v>
+        <v>0.4326</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1475</v>
+        <v>-0.055</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7395</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1515</v>
+        <v>2.4321</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1741</v>
+        <v>2.9449</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0226</v>
+        <v>-0.5128</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6152</v>
+        <v>4.4028</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2805</v>
+        <v>2.786</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3347</v>
+        <v>1.6168</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5045</v>
+        <v>5.5735</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2989</v>
+        <v>3.0873</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2057</v>
+        <v>2.4862</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1107</v>
+        <v>-1.1707</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0184</v>
+        <v>-0.3013</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1291</v>
+        <v>-0.8694</v>
       </c>
       <c r="P5" t="n">
-        <v>0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2038</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3305</v>
+        <v>-0.1262</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1267</v>
+        <v>0.678</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7911</v>
+        <v>2.188</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5808</v>
+        <v>1.9161</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2103</v>
+        <v>0.2719</v>
       </c>
       <c r="G6" t="n">
         <v>1.5173</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0514</v>
+        <v>0.3455</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4795</v>
+        <v>-0.1442</v>
       </c>
       <c r="U6" t="n">
-        <v>0.428</v>
+        <v>0.4897</v>
       </c>
       <c r="V6" t="n">
         <v>0.7602</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>C. CZERAPOWICZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7703</v>
+        <v>0.8667</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1389</v>
+        <v>-0.4945</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3686</v>
+        <v>1.3611</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4481</v>
+        <v>-0.0007</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1223</v>
+        <v>1.3563</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6742</v>
+        <v>-1.357</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3401</v>
+        <v>1.0545</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2679</v>
+        <v>1.9892</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6081</v>
+        <v>-0.9347</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7882</v>
+        <v>-1.0552</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1457</v>
+        <v>-0.6328</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9339</v>
+        <v>-0.4224</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4784</v>
+        <v>0.6276</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7988</v>
+        <v>-0.4614</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3204</v>
+        <v>1.089</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. CZERAPOWICZ</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.6338</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7865</v>
+        <v>2.4747</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7618</v>
+        <v>-1.8409</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0007</v>
+        <v>-0.0337</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3563</v>
+        <v>1.0978</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.357</v>
+        <v>-1.1315</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0545</v>
+        <v>2.1466</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9892</v>
+        <v>1.5147</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9347</v>
+        <v>0.6319</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0552</v>
+        <v>-2.1803</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6328</v>
+        <v>-0.4169</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4224</v>
+        <v>-1.7635</v>
       </c>
       <c r="P8" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7363</v>
+        <v>0.7099</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.3281</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4897</v>
+        <v>0.3818</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8812</v>
+        <v>0.4408</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6297</v>
+        <v>1.686</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7485</v>
+        <v>-1.2453</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0337</v>
+        <v>-0.4481</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0978</v>
+        <v>-1.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1315</v>
+        <v>0.6742</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1466</v>
+        <v>0.3401</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5147</v>
+        <v>-1.2679</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6319</v>
+        <v>1.6081</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1803</v>
+        <v>-0.7882</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4169</v>
+        <v>0.1457</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7635</v>
+        <v>-0.9339</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9574</v>
+        <v>1.1488</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4831</v>
+        <v>1.3459</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4743</v>
+        <v>-0.1971</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7436</v>
+        <v>0.2535</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1825</v>
+        <v>0.4448</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5611</v>
+        <v>-0.1912</v>
       </c>
       <c r="G10" t="n">
         <v>-0.855</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7364000000000001</v>
+        <v>0.2608</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.536</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2004</v>
+        <v>0.1694</v>
       </c>
       <c r="V10" t="n">
         <v>0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4752</v>
+        <v>-0.9049</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5243</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9509</v>
+        <v>-0.8276</v>
       </c>
       <c r="G11" t="n">
         <v>1.2409</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2158</v>
+        <v>0.3545</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1935</v>
+        <v>0.2536</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0224</v>
+        <v>0.1009</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7602</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4964</v>
+        <v>-1.2113</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8911</v>
+        <v>-2.6676</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3947</v>
+        <v>1.4563</v>
       </c>
       <c r="G12" t="n">
         <v>0.2951</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0514</v>
+        <v>0.2337</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.137</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0856</v>
+        <v>0.1472</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7781</v>
+        <v>-1.6287</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7337</v>
+        <v>-0.5535</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0444</v>
+        <v>-1.0752</v>
       </c>
       <c r="G13" t="n">
         <v>1.212</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0326</v>
+        <v>0.1169</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.399</v>
+        <v>-0.2187</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3664</v>
+        <v>0.3356</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5649999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.4458</v>
+        <v>12.7883</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5496</v>
+        <v>11.8919</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8961999999999999</v>
+        <v>0.8962999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>16.6627</v>
@@ -1516,7 +1516,7 @@
         <v>13.2601</v>
       </c>
       <c r="I14" t="n">
-        <v>3.402499999999999</v>
+        <v>3.4025</v>
       </c>
       <c r="J14" t="n">
         <v>25.1347</v>
@@ -1546,13 +1546,13 @@
         <v>11.9626</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7202</v>
+        <v>6.0626</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6883</v>
+        <v>2.0309</v>
       </c>
       <c r="U14" t="n">
-        <v>4.031599999999999</v>
+        <v>4.031400000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-4.4993</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2342</v>
+        <v>3.5437</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2937</v>
+        <v>3.1819</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0595</v>
+        <v>0.3618</v>
       </c>
       <c r="G15" t="n">
         <v>1.3428</v>
@@ -1624,13 +1624,13 @@
         <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.6032</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1526</v>
+        <v>0.0409</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0654</v>
+        <v>-0.6441</v>
       </c>
       <c r="V15" t="n">
         <v>2.8042</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9936</v>
+        <v>1.9595</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7522</v>
+        <v>4.1993</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7587</v>
+        <v>-2.2398</v>
       </c>
       <c r="G16" t="n">
         <v>0.8941</v>
@@ -1702,13 +1702,13 @@
         <v>3.2626</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8804</v>
+        <v>-0.9145</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4949</v>
+        <v>-1.0479</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3855</v>
+        <v>0.1334</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1952</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3307</v>
+        <v>0.3077</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8235</v>
+        <v>1.1588</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1541</v>
+        <v>-0.851</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2056</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9728</v>
+        <v>-0.3344</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1815</v>
+        <v>0.1538</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7913</v>
+        <v>-0.4882</v>
       </c>
       <c r="V17" t="n">
         <v>0.1952</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5821</v>
+        <v>-0.5343</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3082</v>
+        <v>-0.293</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.274</v>
+        <v>-0.2413</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9724</v>
+        <v>-0.5261</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1468</v>
+        <v>-0.2464</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8255</v>
+        <v>-0.2797</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0878</v>
+        <v>0.0747</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2775</v>
+        <v>0.0365</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1896</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0602</v>
+        <v>-0.6009</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.4243</v>
+        <v>-0.2829</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6359</v>
+        <v>-0.318</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6953</v>
+        <v>-0.4431</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3509</v>
+        <v>-0.1502</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0462</v>
+        <v>-0.2929</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8875</v>
+        <v>-0.8935</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4047</v>
+        <v>-0.337</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4828</v>
+        <v>-0.5565</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5261</v>
+        <v>-0.9751</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2464</v>
+        <v>-0.1336</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2797</v>
+        <v>-0.8415</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0747</v>
+        <v>0.5917</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0365</v>
+        <v>0.6482</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>-0.0566</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6009</v>
+        <v>-1.5668</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2829</v>
+        <v>-0.7819</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.318</v>
+        <v>-0.7849</v>
       </c>
       <c r="P19" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7964</v>
+        <v>-0.7009</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.262</v>
+        <v>-0.1887</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5344</v>
+        <v>-0.5122</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>J. LOPEZ SANTANA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2853</v>
+        <v>-1.2451</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6723</v>
+        <v>-0.619</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.613</v>
+        <v>-0.6261</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9751</v>
+        <v>-5.2079</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1336</v>
+        <v>-2.5241</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8415</v>
+        <v>-2.6838</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5917</v>
+        <v>-1.7477</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6482</v>
+        <v>-0.3158</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0566</v>
+        <v>-1.4319</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5668</v>
+        <v>-3.4602</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7819</v>
+        <v>-2.2083</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7849</v>
+        <v>-1.2519</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0927</v>
+        <v>-0.2971</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5239</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5688</v>
+        <v>0.5068</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5649999999999999</v>
+        <v>3.3899</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5649999999999999</v>
+        <v>3.0202</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANTANA</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6485</v>
+        <v>-1.3489</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8426</v>
+        <v>-0.6434</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.7055</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.2079</v>
+        <v>-1.9724</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5241</v>
+        <v>-1.1468</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6838</v>
+        <v>-0.8255</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7477</v>
+        <v>1.0878</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3158</v>
+        <v>1.2775</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4319</v>
+        <v>-0.1896</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4602</v>
+        <v>-3.0602</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2083</v>
+        <v>-2.4243</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2519</v>
+        <v>-0.6359</v>
       </c>
       <c r="P21" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7005</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0274</v>
+        <v>-0.6862</v>
       </c>
       <c r="U21" t="n">
-        <v>0.327</v>
+        <v>0.6147</v>
       </c>
       <c r="V21" t="n">
-        <v>3.3899</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>3.0202</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1368</v>
+        <v>-2.7312</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6024</v>
+        <v>-1.5506</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5344</v>
+        <v>-1.1806</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0054</v>
+        <v>-2.4965</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.5886</v>
+        <v>-1.1921</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4168</v>
+        <v>-1.3045</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6251</v>
+        <v>-1.4136</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9948</v>
+        <v>-1.4901</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6303</v>
+        <v>0.0765</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3803</v>
+        <v>-1.0829</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5939</v>
+        <v>0.298</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2136</v>
+        <v>-1.381</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5412</v>
+        <v>-0.0171</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0227</v>
+        <v>0.0805</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4814</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7549</v>
+        <v>-2.955</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8201</v>
+        <v>-2.3847</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9348</v>
+        <v>-0.5703</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0498</v>
+        <v>-4.0054</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7543</v>
+        <v>-3.5886</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8041</v>
+        <v>-0.4168</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5139</v>
+        <v>-2.6251</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4486</v>
+        <v>-1.9948</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9347</v>
+        <v>-0.6303</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5637</v>
+        <v>-1.3803</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6943</v>
+        <v>-1.5939</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8694</v>
+        <v>0.2136</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5772</v>
+        <v>-0.277</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4194</v>
+        <v>0.2403</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9966</v>
+        <v>-0.5173</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.0647</v>
+        <v>-0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.911</v>
+        <v>-3.3059</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5506</v>
+        <v>-2.1554</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3604</v>
+        <v>-1.1506</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4965</v>
+        <v>-1.0498</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1921</v>
+        <v>0.7543</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3045</v>
+        <v>-1.8041</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4136</v>
+        <v>1.5139</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4901</v>
+        <v>2.4486</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0765</v>
+        <v>-0.9347</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0829</v>
+        <v>-2.5637</v>
       </c>
       <c r="N24" t="n">
-        <v>0.298</v>
+        <v>-1.6943</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.381</v>
+        <v>-0.8694</v>
       </c>
       <c r="P24" t="n">
         <v>-0.2175</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.9576</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.197</v>
+        <v>0.0261</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0805</v>
+        <v>-0.7547</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2775</v>
+        <v>0.7808</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.0647</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1369</v>
+        <v>-3.7528</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5649</v>
+        <v>-1.4531</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.572</v>
+        <v>-2.2997</v>
       </c>
       <c r="G25" t="n">
         <v>-2.4606</v>
@@ -2404,13 +2404,13 @@
         <v>1.5225</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9813</v>
+        <v>-0.5972</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0274</v>
+        <v>-0.9157</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0461</v>
+        <v>0.3184</v>
       </c>
       <c r="V25" t="n">
         <v>-1.13</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.4459</v>
+        <v>-10.9558</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.8964000000000008</v>
+        <v>-0.8962000000000008</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.5496</v>
+        <v>-10.0596</v>
       </c>
       <c r="G26" t="n">
         <v>-16.6625</v>
@@ -2455,13 +2455,13 @@
         <v>-3.402600000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>8.472099999999999</v>
+        <v>8.472100000000001</v>
       </c>
       <c r="K26" t="n">
         <v>1.6907</v>
       </c>
       <c r="L26" t="n">
-        <v>6.7814</v>
+        <v>6.781400000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-25.1348</v>
@@ -2473,7 +2473,7 @@
         <v>-10.184</v>
       </c>
       <c r="P26" t="n">
-        <v>5.437599999999999</v>
+        <v>5.4376</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.9628</v>
@@ -2482,13 +2482,13 @@
         <v>17.4005</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.720199999999999</v>
+        <v>-4.229900000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.031600000000001</v>
+        <v>-4.0318</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.6884</v>
+        <v>-0.1982</v>
       </c>
       <c r="V26" t="n">
         <v>4.499199999999999</v>
